--- a/docs/EXECUTION_SURFACES.xlsx
+++ b/docs/EXECUTION_SURFACES.xlsx
@@ -529,10 +529,10 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="92" customHeight="1">
+    <row r="2" ht="118" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Verdict: from the acquisition of the code to the last step, motion A (zip or clone → VS Code → Polyglot notebooks) yields the same artefacts as motions B (WezTerm → Ubuntu terminal) and C (Cloud Shell), because every step cell runs the same scripts/run_pass1.sh inside an Ubuntu that the same bootstrap provisioned, against the same BigQuery project, Drive root and HubSpot portal. The layers that are NOT parallel are all outside the pipeline itself: acquiring and updating the code (a zip has no git), file modes, package provisioning, and the locality of the SQLite ledger for the live HubSpot steps. Each has a remediation in the Layers sheet.</t>
+          <t>Verdict: from the acquisition of the code to the last step, motion A (zip or clone → VS Code → Polyglot notebooks) yields the same artefacts as motions B (WezTerm → Ubuntu terminal) and C (Cloud Shell), because every step cell runs the same scripts/run_pass1.sh inside an Ubuntu that the same bootstrap provisioned, against the same BigQuery project, Drive root and HubSpot portal. The layers that are NOT parallel are all outside the pipeline itself: acquiring and updating the code (a zip has no git), file modes, package provisioning, and the locality of the SQLite ledger for the live HubSpot steps. Each has a remediation in the Layers sheet. Reconciled through pass 2 on 2026-09-30: the orphan salvage (6f38600) and the BigQuery materialisation of the HubSpot import files (765cd01) were run from Cloud Shell and probed with bq query — the table is the same from every surface. See Layers L14–L15, Pipeline steps 15b–15c, Remediation R21–R25, the last four Equality checks, and docs/EXECUTION_SURFACES.md for the narrative.</t>
         </is>
       </c>
     </row>
@@ -786,7 +786,7 @@
     <row r="17" ht="78" customHeight="1">
       <c r="A17" s="11" t="inlineStr">
         <is>
-          <t>Legend: Parity column colours — green Parallel, yellow Conditional, orange Divergent. Layers L0–L13 are the execution layer subdivided from acquisition to updates; Pipeline steps are the 16 runner steps plus status and rollback; Remediation is the catalogue of observed and simulated failures (R01–R20); Equality checks lists what to compare between two surfaces after each stage. Source: the mr-load repository on branch claude/mr-load-library-system-dphpbj at 2026-09-27, the Cloud Shell logs shared on 2026-09-14/15, and simulations run in the development container (non-git folder, in-place conversion, relative state dir).</t>
+          <t>Legend: Parity column colours — green Parallel, yellow Conditional, orange Divergent. Layers L0–L15 are the execution layer subdivided from acquisition to updates; Pipeline steps are the 16 runner steps plus the pass-2 wizard route (15b–15c), status and rollback; Remediation is the catalogue of observed and simulated failures (R01–R25); Equality checks lists what to compare between two surfaces after each stage. Source: the mr-load repository on branch claude/mr-load-library-system-dphpbj at 2026-09-30 (765cd01), the Cloud Shell logs shared on 2026-09-14/15, and simulations run in the development container (non-git folder, in-place conversion, relative state dir).</t>
         </is>
       </c>
     </row>
@@ -805,7 +805,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1524,6 +1524,100 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>L14</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>Pass-2 decisions: view and edit review/deal_decisions.csv</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>VS Code on the clone (Rainbow CSV) — the file is under .mrload/review/ of the WSL or Windows clone; or Invoke-Ubuntu 'column -s, -t &lt; .mrload/review/deal_decisions.csv' to print it.</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>column -s, -t &lt; .mrload/review/deal_decisions.csv | less -S (← → scroll, q); edit with nano or VS Code (WSL remote).</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>cloudshell edit .mrload/review/deal_decisions.csv (Cloud Shell Editor, Ctrl+S); or nano; view with column -s, -t &lt; … | less -S; or cloudshell download &lt;file&gt; → edit on the laptop → ⋮ Upload → mv ~/deal_decisions.csv ~/mir-load/.mrload/review/</t>
+        </is>
+      </c>
+      <c r="F16" s="13" t="inlineStr">
+        <is>
+          <t>Conditional</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>The file is per clone (L9): edit it on the surface that will run deals-dry / deals-live. Cloud Shell has no desktop editor, hence cloudshell edit or the download/upload round trip. column misaligns a row whose quoted field contains a comma (glance only). The writer emits CRLF; the reader accepts LF, CRLF or a mix, so any editor is fine.</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>None needed. Bulk approve of every row: sed -i -E '2,$ s/,N,([^,]*)\r?$/,Y,\1/' .mrload/review/deal_decisions.csv (approve is the 15th column, before operator_note). Per-row approval is the point of the file, so prefer the editor.</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>Cloud Shell run of 2026-09-30: review → edit → deals-dry → ledger-export; the rehearsal flips approve on the same file layout.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>L15</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>BigQuery materialisation of the HubSpot import files + probe</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>Invoke-Step 'ledger-export' (LIVE BQ_LOAD) loads review/hubspot_deals_import.csv and hubspot_companies_import.csv as mrload_raw.hubspot_deals_import / hubspot_companies_import; probe: Invoke-Ubuntu 'bq query --use_legacy_sql=false "select dealname, company_name, company_hs_object_id, op_company_status, op_approve, hs_object_id from \`wisekeybq.mrload_raw.hubspot_deals_import\` order by company_name, dealname"'</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>scripts/run_pass1.sh ledger-export; probe: bq query --use_legacy_sql=false 'SELECT dealname, company_name, company_hs_object_id, op_company_status, op_approve, hs_object_id FROM `wisekeybq.mrload_raw.hubspot_deals_import` ORDER BY company_name, dealname'</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>Same commands; bq is preauthenticated in Cloud Shell. Wizard file without the console: bq query --use_legacy_sql=false --format=csv --max_rows=100000 '&lt;the query the step printed&gt;' &gt; ~/hubspot_deals_import.csv &amp;&amp; cloudshell download ~/hubspot_deals_import.csv</t>
+        </is>
+      </c>
+      <c r="F17" s="14" t="inlineStr">
+        <is>
+          <t>Parallel</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>None: the two tables are shared truth (L11) for the import files, so the wizard's input no longer depends on a clone's review/ folder or on a file transfer. They mirror the ledger of the clone that ran ledger-export (L9) plus that clone's deal_decisions.csv; deals-dry outcomes that are not persisted (would_create) do not appear.</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>Console route: BigQuery console → SELECT * EXCEPT(pipeline, dealstage, op_company_status, op_api_status, op_api_error) … WHERE op_approve = 'Y' → Save results → Sheets/CSV → HubSpot Import (hs_object_id → Deals·Record ID, company_hs_object_id → Companies·Record ID). Loader route: deals-live creates and associates the salvaged deals through the API (no Cloud Function needed).</t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>Probe of 2026-09-30 on the sandbox (portal 49610528) from Cloud Shell: 10 rows = the 10 inferred anchors; 4 ELTA rows salvaged (op_company_status salvaged, company_hs_object_id 35988056623 found by name, never created); 6 resolved from pass 1; op_approve N and hs_object_id NULL everywhere (no deal created yet). Row for row the content of review/hubspot_deals_import.csv (rehearsal check 47: byte-identical load).</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1535,7 +1629,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2177,12 +2271,12 @@
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>hs_company_id / hs_note_id populated in silver</t>
+          <t>hs_company_id / hs_note_id populated in silver; mrload_raw.hubspot_deals_import / hubspot_companies_import loaded (schema JSONs in .mrload/ledger_export/)</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>Exports THIS clone's ledger: run it from the surface that ran the live steps.</t>
+          <t>Exports THIS clone's ledger: run it from the surface that ran the live steps. Also regenerates the two import files from ledger + deal_decisions.csv and prints the console query for the wizard route.</t>
         </is>
       </c>
     </row>
@@ -2218,42 +2312,44 @@
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>would_create per approved anchor; notes count per deal</t>
+          <t>would_create per approved anchor; notes count per deal; companies_resolved *_pass2 statuses persisted (salvage runs in dry mode too)</t>
         </is>
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>Reads deal_decisions.csv of that clone (edit it there).</t>
+          <t>Reads deal_decisions.csv of that clone (edit it there: L14). Orphan companies are searched by name, never created.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="n">
-        <v>16</v>
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>15b</t>
+        </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>deals-live</t>
+          <t>ledger-export (import tables, wizard route)</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>LIVE DEAL_CREATE</t>
+          <t>LIVE BQ_LOAD</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>Invoke-Step 'deals-live'</t>
+          <t>Invoke-Step 'ledger-export'</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>scripts/run_pass1.sh deals-live</t>
+          <t>scripts/run_pass1.sh ledger-export</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>scripts/run_pass1.sh deals-live</t>
+          <t>scripts/run_pass1.sh ledger-export</t>
         </is>
       </c>
       <c r="G17" s="13" t="inlineStr">
@@ -2263,141 +2359,229 @@
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>ledger deals_created created=N; deal→company and note→deal associations</t>
+          <t>mrload_raw.hubspot_deals_import: one row per inferred anchor, company_hs_object_id filled for resolved AND salvaged companies; hubspot_companies_import: the companies confirmed missing</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>Ledger-keyed (L9); one deal per inferred anchor.</t>
+          <t>Optional branch after deals-dry when the deals go through the HubSpot Import wizard (BigQuery console → Save results) instead of deals-live. Does not make pass 2 stale in pipeline_state.sh; its 'next' hint still proposes deals-live. Ledger condition as row 14.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="n">
-        <v>17</v>
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>15c</t>
+        </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>ledger-export (again)</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>LIVE BQ_LOAD</t>
-        </is>
-      </c>
+          <t>BigQuery probe of the import tables</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr"/>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>Invoke-Step 'ledger-export'</t>
+          <t>Invoke-Ubuntu 'bq query --use_legacy_sql=false "select dealname, company_name, company_hs_object_id, op_company_status, op_approve, hs_object_id from \`wisekeybq.mrload_raw.hubspot_deals_import\` order by company_name, dealname"'</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>scripts/run_pass1.sh ledger-export</t>
+          <t>bq query --use_legacy_sql=false 'SELECT dealname, company_name, company_hs_object_id, op_company_status, op_approve, hs_object_id FROM `wisekeybq.mrload_raw.hubspot_deals_import` ORDER BY company_name, dealname'</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>scripts/run_pass1.sh ledger-export</t>
-        </is>
-      </c>
-      <c r="G18" s="13" t="inlineStr">
-        <is>
-          <t>Conditional</t>
+          <t>bq query --use_legacy_sql=false 'SELECT dealname, company_name, company_hs_object_id, op_company_status, op_approve, hs_object_id FROM `wisekeybq.mrload_raw.hubspot_deals_import` ORDER BY company_name, dealname'</t>
+        </is>
+      </c>
+      <c r="G18" s="14" t="inlineStr">
+        <is>
+          <t>Parallel</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>silver_library_deal.hs_deal_id populated</t>
+          <t>the table above — identical from every surface (bq reads the same dataset)</t>
         </is>
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>Closes the loop after pass 2.</t>
+          <t>Probe of 2026-09-30 on the sandbox (portal 49610528) from Cloud Shell: 10 rows = the 10 inferred anchors; 4 ELTA rows salvaged (op_company_status salvaged, company_hs_object_id 35988056623 found by name, never created); 6 resolved from pass 1; op_approve N and hs_object_id NULL everywhere (no deal created yet). Row for row the content of review/hubspot_deals_import.csv (rehearsal check 47: byte-identical load).</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>status / where am I</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr"/>
+          <t>deals-live</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>LIVE DEAL_CREATE</t>
+        </is>
+      </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>Invoke-Step 'status'; Get-PipelineState</t>
+          <t>Invoke-Step 'deals-live'</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>scripts/run_pass1.sh status; scripts/dev/pipeline_state.sh</t>
+          <t>scripts/run_pass1.sh deals-live</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>scripts/run_pass1.sh status; scripts/dev/pipeline_state.sh</t>
-        </is>
-      </c>
-      <c r="G19" s="14" t="inlineStr">
-        <is>
-          <t>Parallel</t>
+          <t>scripts/run_pass1.sh deals-live</t>
+        </is>
+      </c>
+      <c r="G19" s="13" t="inlineStr">
+        <is>
+          <t>Conditional</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>same done/pending picture per clone</t>
+          <t>ledger deals_created created=N; deal→company and note→deal associations</t>
         </is>
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>Checkpoints are per clone (L9).</t>
+          <t>Ledger-keyed (L9); one deal per inferred anchor. This is the programmatic loader for the salvaged deals too: an approved row whose company was salvaged is created and associated to that company id (no Cloud Function needed). create_error = pipeline / dealstage is not an id of THIS portal (R21).</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>ledger-export (again)</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>LIVE BQ_LOAD</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>Invoke-Step 'ledger-export'</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>scripts/run_pass1.sh ledger-export</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>scripts/run_pass1.sh ledger-export</t>
+        </is>
+      </c>
+      <c r="G20" s="13" t="inlineStr">
+        <is>
+          <t>Conditional</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>silver_library_deal.hs_deal_id populated; hubspot_deals_import.hs_object_id filled and op_api_status = created</t>
+        </is>
+      </c>
+      <c r="I20" s="4" t="inlineStr">
+        <is>
+          <t>Closes the loop after pass 2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>status / where am I</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr"/>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>Invoke-Step 'status'; Get-PipelineState</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>scripts/run_pass1.sh status; scripts/dev/pipeline_state.sh</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>scripts/run_pass1.sh status; scripts/dev/pipeline_state.sh</t>
+        </is>
+      </c>
+      <c r="G21" s="14" t="inlineStr">
+        <is>
+          <t>Parallel</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>same done/pending picture per clone</t>
+        </is>
+      </c>
+      <c r="I21" s="4" t="inlineStr">
+        <is>
+          <t>Checkpoints are per clone (L9).</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="n">
         <v>19</v>
       </c>
-      <c r="B20" s="4" t="inlineStr">
+      <c r="B22" s="4" t="inlineStr">
         <is>
           <t>unmigrate (rollback)</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr">
+      <c r="C22" s="4" t="inlineStr">
         <is>
           <t>LIVE UNMIGRATE</t>
         </is>
       </c>
-      <c r="D20" s="4" t="inlineStr">
+      <c r="D22" s="4" t="inlineStr">
         <is>
           <t>Invoke-Step 'unmigrate'</t>
         </is>
       </c>
-      <c r="E20" s="4" t="inlineStr">
+      <c r="E22" s="4" t="inlineStr">
         <is>
           <t>scripts/run_pass1.sh unmigrate</t>
         </is>
       </c>
-      <c r="F20" s="4" t="inlineStr">
+      <c r="F22" s="4" t="inlineStr">
         <is>
           <t>scripts/run_pass1.sh unmigrate</t>
         </is>
       </c>
-      <c r="G20" s="13" t="inlineStr">
+      <c r="G22" s="13" t="inlineStr">
         <is>
           <t>Conditional</t>
         </is>
       </c>
-      <c r="H20" s="4" t="inlineStr">
+      <c r="H22" s="4" t="inlineStr">
         <is>
           <t>notes deleted per the ledger</t>
         </is>
       </c>
-      <c r="I20" s="4" t="inlineStr">
+      <c r="I22" s="4" t="inlineStr">
         <is>
           <t>Uses the ledger of the clone that attached them.</t>
         </is>
@@ -2414,7 +2598,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3203,6 +3387,193 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>R21</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>deals-dry / deals-live: failed ×N, error create_error</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>A B C</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>dealstage / pipeline value is not a STAGE / PIPELINE ID of the portal the token belongs to (sandbox ids differ from production).</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>Read the ids once: set -a; source .env; set +a; curl -s -H "Authorization: Bearer $HUBSPOT_SANDBOX_TOKEN" https://api.hubapi.com/crm/v3/pipelines/deals | python3 -c 'import json,sys
+for p in json.load(sys.stdin)["results"]:
+    print(p["id"], p["label"]); [print("   ", s["id"], s["label"]) for s in p["stages"]]' — then fill pipeline / dealstage in deal_decisions.csv or set MRLOAD_DEAL_PIPELINE / MRLOAD_DEAL_STAGE.</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t>sandbox pass 2 (6 failed rows); deals_summary prints the hint</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>R22</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>deals-dry: no_company_resolved on rows whose company folder is year-prefixed (2021_ELTA, 2022_Aselsan)</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>A B C</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>Pass 1 never resolves engagement folders (companies.py filters company_folder); before 6f38600 pass 2 had no company to associate with.</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>git pull (6f38600): pass 2 salvages by searching the remainder name (ELTA); found → matched_by_name_pass2 and the deal associates to it; not found → not_in_portal_pass2 and a hubspot_companies_import row. The pipeline never creates the company.</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t>sandbox 2026-09-30: 4 ELTA rows salvaged → company 35988056623</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>R23</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>The HubSpot import CSVs cannot be handed to the wizard from Cloud Shell</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>L9 / L11</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>The files live in the Cloud Shell clone's .mrload/review/; no desktop, no file transfer to the browser that runs the wizard.</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>git pull (765cd01): ledger-export loads them as mrload_raw.hubspot_deals_import / hubspot_companies_import. Console: query → Save results → Sheets/CSV → Import. Terminal: bq query --use_legacy_sql=false --format=csv --max_rows=100000 '…' &gt; ~/f.csv &amp;&amp; cloudshell download ~/f.csv</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="inlineStr">
+        <is>
+          <t>probe 2026-09-30; rehearsal checks 46–47</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>R24</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>How to look at or edit a review CSV on Cloud Shell</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>No desktop editor; column -s, -t misaligns a row whose quoted field contains a comma.</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>cloudshell edit &lt;file&gt; (Cloud Shell Editor) or nano to edit; column -s, -t &lt; &lt;file&gt; | less -S for a glance; less -S &lt;file&gt; for the exact text; cloudshell download &lt;file&gt; then ⋮ Upload and mv ~/&lt;file&gt; ~/mir-load/.mrload/review/ for a laptop round trip.</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="inlineStr">
+        <is>
+          <t>this session (L14)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>R25</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>A company-level working folder (Drafts/pre-PO) became a HubSpot company in pass 1 and anchors a deal</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>A B C</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>The walker classifies every folder at company level as company_folder unless its name is year-prefixed; companies-live created it in the sandbox.</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>Before the production walk: add the folder to the exclusions in context/cards/library.yaml, delete the sandbox company, re-run walk → bq-load → dbt → review. Not done yet — flagged from the probe.</t>
+        </is>
+      </c>
+      <c r="G26" s="4" t="inlineStr">
+        <is>
+          <t>probe 2026-09-30 (row 1: company_name Drafts/pre-PO, id 58614964830)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3214,7 +3585,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3492,6 +3863,114 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>after deals-dry</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>salvage statuses in the ledger</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>Invoke-Ubuntu 'scripts/run_pass1.sh status'</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>scripts/run_pass1.sh status</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>companies_resolved: matched_by_name_pass2 = salvaged companies (ELTA), not_in_portal_pass2 = rows of hubspot_companies_import</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>after ledger-export</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>the import tables (the wizard's input)</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>Invoke-Ubuntu 'bq query --use_legacy_sql=false "select dealname, company_name, company_hs_object_id, op_company_status, op_approve, hs_object_id from \`wisekeybq.mrload_raw.hubspot_deals_import\` order by company_name, dealname"'</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>bq query --use_legacy_sql=false 'SELECT dealname, company_name, company_hs_object_id, op_company_status, op_approve, hs_object_id FROM `wisekeybq.mrload_raw.hubspot_deals_import` ORDER BY company_name, dealname'</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>one row per inferred anchor; company_hs_object_id on resolved and salvaged rows; hs_object_id NULL until deals-live or the wizard import; identical from every surface (2026-09-30: 10 rows, 4 salvaged, 6 resolved)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>after ledger-export</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>table == review file</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>Invoke-Ubuntu 'bq query --use_legacy_sql=false "select count(*) n from \`wisekeybq.mrload_raw.hubspot_deals_import\`"; wc -l .mrload/review/hubspot_deals_import.csv'</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>bq query --use_legacy_sql=false 'select count(*) n from `wisekeybq.mrload_raw.hubspot_deals_import`'; wc -l .mrload/review/hubspot_deals_import.csv</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>n = CSV lines − 1 (rehearsal check 47: the loaded copy is byte-identical to the review file)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>after deals-live + ledger-export</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>Record IDs written back</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>Invoke-Ubuntu 'bq query --use_legacy_sql=false "select dealname, company_name, company_hs_object_id, op_company_status, op_approve, hs_object_id from \`wisekeybq.mrload_raw.hubspot_deals_import\` order by company_name, dealname"'</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>bq query --use_legacy_sql=false 'SELECT dealname, company_name, company_hs_object_id, op_company_status, op_approve, hs_object_id FROM `wisekeybq.mrload_raw.hubspot_deals_import` ORDER BY company_name, dealname'</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>hs_object_id filled and op_api_status = created on the rows deals-live created; the same query on every surface</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/EXECUTION_SURFACES.xlsx
+++ b/docs/EXECUTION_SURFACES.xlsx
@@ -32,11 +32,16 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Arial"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
       <sz val="10"/>
     </font>
     <font>
@@ -46,12 +51,6 @@
     </font>
     <font>
       <name val="Arial"/>
-      <b val="1"/>
-      <sz val="14"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <i val="1"/>
       <color rgb="00555555"/>
       <sz val="9"/>
     </font>
@@ -70,7 +69,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F8CBAD"/>
+        <fgColor rgb="00E2F0D9"/>
       </patternFill>
     </fill>
     <fill>
@@ -80,7 +79,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E2F0D9"/>
+        <fgColor rgb="00F8CBAD"/>
       </patternFill>
     </fill>
   </fills>
@@ -110,40 +109,32 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -529,7 +520,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="118" customHeight="1">
+    <row r="2" ht="120" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Verdict: from the acquisition of the code to the last step, motion A (zip or clone → VS Code → Polyglot notebooks) yields the same artefacts as motions B (WezTerm → Ubuntu terminal) and C (Cloud Shell), because every step cell runs the same scripts/run_pass1.sh inside an Ubuntu that the same bootstrap provisioned, against the same BigQuery project, Drive root and HubSpot portal. The layers that are NOT parallel are all outside the pipeline itself: acquiring and updating the code (a zip has no git), file modes, package provisioning, and the locality of the SQLite ledger for the live HubSpot steps. Each has a remediation in the Layers sheet. Reconciled through pass 2 on 2026-09-30: the orphan salvage (6f38600) and the BigQuery materialisation of the HubSpot import files (765cd01) were run from Cloud Shell and probed with bq query — the table is the same from every surface. See Layers L14–L15, Pipeline steps 15b–15c, Remediation R21–R25, the last four Equality checks, and docs/EXECUTION_SURFACES.md for the narrative.</t>
@@ -672,29 +663,29 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>Layers</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>Pipeline steps</t>
         </is>
       </c>
-      <c r="D10" s="6" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>Meaning</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="inlineStr">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>Parallel</t>
         </is>
@@ -714,7 +705,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="inlineStr">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>Conditional</t>
         </is>
@@ -734,7 +725,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="9" t="inlineStr">
+      <c r="A13" s="8" t="inlineStr">
         <is>
           <t>Divergent</t>
         </is>
@@ -754,37 +745,39 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="inlineStr">
+      <c r="A14" s="9" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B14" s="5">
+      <c r="B14" s="4">
         <f>SUM(B11:B13)</f>
         <v/>
       </c>
-      <c r="C14" s="5">
+      <c r="C14" s="4">
         <f>SUM(C11:C13)</f>
         <v/>
       </c>
+      <c r="D14" s="4" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="10" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>Rows on the sheet (must equal Total)</t>
         </is>
       </c>
-      <c r="B15" s="10">
+      <c r="B15" s="4">
         <f>COUNTA(Layers!$A:$A)-1</f>
         <v/>
       </c>
-      <c r="C15" s="10">
+      <c r="C15" s="4">
         <f>COUNTA('Pipeline steps'!$A:$A)-1</f>
         <v/>
       </c>
-    </row>
-    <row r="17" ht="78" customHeight="1">
-      <c r="A17" s="11" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr"/>
+    </row>
+    <row r="17" ht="90" customHeight="1">
+      <c r="A17" s="10" t="inlineStr">
         <is>
           <t>Legend: Parity column colours — green Parallel, yellow Conditional, orange Divergent. Layers L0–L15 are the execution layer subdivided from acquisition to updates; Pipeline steps are the 16 runner steps plus the pass-2 wizard route (15b–15c), status and rollback; Remediation is the catalogue of observed and simulated failures (R01–R25); Equality checks lists what to compare between two surfaces after each stage. Source: the mr-load repository on branch claude/mr-load-library-system-dphpbj at 2026-09-30 (765cd01), the Cloud Shell logs shared on 2026-09-14/15, and simulations run in the development container (non-git folder, in-place conversion, relative state dir).</t>
         </is>
@@ -892,7 +885,7 @@
           <t>git clone https://github.com/Wkayaobama/mir-load.git ~/mir-load in the persistent home.</t>
         </is>
       </c>
-      <c r="F2" s="12" t="inlineStr">
+      <c r="F2" s="8" t="inlineStr">
         <is>
           <t>Divergent</t>
         </is>
@@ -939,7 +932,7 @@
           <t>same as B</t>
         </is>
       </c>
-      <c r="F3" s="13" t="inlineStr">
+      <c r="F3" s="7" t="inlineStr">
         <is>
           <t>Conditional</t>
         </is>
@@ -986,7 +979,7 @@
           <t>Linux clone: LF and modes from the index.</t>
         </is>
       </c>
-      <c r="F4" s="13" t="inlineStr">
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>Conditional</t>
         </is>
@@ -1033,7 +1026,7 @@
           <t>Cloud Shell VM (Debian-based, gcloud and bq preinstalled, home persists, VM ephemeral).</t>
         </is>
       </c>
-      <c r="F5" s="14" t="inlineStr">
+      <c r="F5" s="6" t="inlineStr">
         <is>
           <t>Parallel</t>
         </is>
@@ -1080,7 +1073,7 @@
           <t>Observed: packages in ~/.local (pip --user, python3.12) rather than a venv; same requirements files, versions resolved on a different day.</t>
         </is>
       </c>
-      <c r="F6" s="13" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>Conditional</t>
         </is>
@@ -1127,7 +1120,7 @@
           <t>scripts/gauth.sh too: Cloud Shell's built-in credentials carry the cloud-platform scope, not Drive.</t>
         </is>
       </c>
-      <c r="F7" s="14" t="inlineStr">
+      <c r="F7" s="6" t="inlineStr">
         <is>
           <t>Parallel</t>
         </is>
@@ -1174,7 +1167,7 @@
           <t>Same as B.</t>
         </is>
       </c>
-      <c r="F8" s="14" t="inlineStr">
+      <c r="F8" s="6" t="inlineStr">
         <is>
           <t>Parallel</t>
         </is>
@@ -1221,7 +1214,7 @@
           <t>Same as B.</t>
         </is>
       </c>
-      <c r="F9" s="12" t="inlineStr">
+      <c r="F9" s="8" t="inlineStr">
         <is>
           <t>Divergent</t>
         </is>
@@ -1268,7 +1261,7 @@
           <t>Same as B.</t>
         </is>
       </c>
-      <c r="F10" s="14" t="inlineStr">
+      <c r="F10" s="6" t="inlineStr">
         <is>
           <t>Parallel</t>
         </is>
@@ -1315,7 +1308,7 @@
           <t>.mrload/ of the Cloud Shell clone.</t>
         </is>
       </c>
-      <c r="F11" s="12" t="inlineStr">
+      <c r="F11" s="8" t="inlineStr">
         <is>
           <t>Divergent</t>
         </is>
@@ -1362,7 +1355,7 @@
           <t>Same as B.</t>
         </is>
       </c>
-      <c r="F12" s="14" t="inlineStr">
+      <c r="F12" s="6" t="inlineStr">
         <is>
           <t>Parallel</t>
         </is>
@@ -1409,7 +1402,7 @@
           <t>Same.</t>
         </is>
       </c>
-      <c r="F13" s="14" t="inlineStr">
+      <c r="F13" s="6" t="inlineStr">
         <is>
           <t>Parallel</t>
         </is>
@@ -1456,7 +1449,7 @@
           <t>Same as B (needs requirements-dev: duckdb, dbt-duckdb).</t>
         </is>
       </c>
-      <c r="F14" s="14" t="inlineStr">
+      <c r="F14" s="6" t="inlineStr">
         <is>
           <t>Parallel</t>
         </is>
@@ -1503,7 +1496,7 @@
           <t>git pull</t>
         </is>
       </c>
-      <c r="F15" s="12" t="inlineStr">
+      <c r="F15" s="8" t="inlineStr">
         <is>
           <t>Divergent</t>
         </is>
@@ -1550,7 +1543,7 @@
           <t>cloudshell edit .mrload/review/deal_decisions.csv (Cloud Shell Editor, Ctrl+S); or nano; view with column -s, -t &lt; … | less -S; or cloudshell download &lt;file&gt; → edit on the laptop → ⋮ Upload → mv ~/deal_decisions.csv ~/mir-load/.mrload/review/</t>
         </is>
       </c>
-      <c r="F16" s="13" t="inlineStr">
+      <c r="F16" s="7" t="inlineStr">
         <is>
           <t>Conditional</t>
         </is>
@@ -1597,7 +1590,7 @@
           <t>Same commands; bq is preauthenticated in Cloud Shell. Wizard file without the console: bq query --use_legacy_sql=false --format=csv --max_rows=100000 '&lt;the query the step printed&gt;' &gt; ~/hubspot_deals_import.csv &amp;&amp; cloudshell download ~/hubspot_deals_import.csv</t>
         </is>
       </c>
-      <c r="F17" s="14" t="inlineStr">
+      <c r="F17" s="6" t="inlineStr">
         <is>
           <t>Parallel</t>
         </is>
@@ -1715,7 +1708,7 @@
           <t>scripts/run_pass1.sh preflight</t>
         </is>
       </c>
-      <c r="G2" s="14" t="inlineStr">
+      <c r="G2" s="6" t="inlineStr">
         <is>
           <t>Parallel</t>
         </is>
@@ -1756,7 +1749,7 @@
           <t>scripts/run_pass1.sh walk</t>
         </is>
       </c>
-      <c r="G3" s="14" t="inlineStr">
+      <c r="G3" s="6" t="inlineStr">
         <is>
           <t>Parallel</t>
         </is>
@@ -1797,7 +1790,7 @@
           <t>scripts/run_pass1.sh bq-init</t>
         </is>
       </c>
-      <c r="G4" s="14" t="inlineStr">
+      <c r="G4" s="6" t="inlineStr">
         <is>
           <t>Parallel</t>
         </is>
@@ -1842,7 +1835,7 @@
           <t>scripts/run_pass1.sh bq-load (type YES)</t>
         </is>
       </c>
-      <c r="G5" s="14" t="inlineStr">
+      <c r="G5" s="6" t="inlineStr">
         <is>
           <t>Parallel</t>
         </is>
@@ -1887,7 +1880,7 @@
           <t>scripts/run_pass1.sh hs-props</t>
         </is>
       </c>
-      <c r="G6" s="14" t="inlineStr">
+      <c r="G6" s="6" t="inlineStr">
         <is>
           <t>Parallel</t>
         </is>
@@ -1928,7 +1921,7 @@
           <t>scripts/run_pass1.sh dbt</t>
         </is>
       </c>
-      <c r="G7" s="14" t="inlineStr">
+      <c r="G7" s="6" t="inlineStr">
         <is>
           <t>Parallel</t>
         </is>
@@ -1969,7 +1962,7 @@
           <t>scripts/run_pass1.sh hs-props-verify</t>
         </is>
       </c>
-      <c r="G8" s="14" t="inlineStr">
+      <c r="G8" s="6" t="inlineStr">
         <is>
           <t>Parallel</t>
         </is>
@@ -2010,7 +2003,7 @@
           <t>scripts/run_pass1.sh review</t>
         </is>
       </c>
-      <c r="G9" s="14" t="inlineStr">
+      <c r="G9" s="6" t="inlineStr">
         <is>
           <t>Parallel</t>
         </is>
@@ -2051,7 +2044,7 @@
           <t>scripts/run_pass1.sh companies-dry</t>
         </is>
       </c>
-      <c r="G10" s="14" t="inlineStr">
+      <c r="G10" s="6" t="inlineStr">
         <is>
           <t>Parallel</t>
         </is>
@@ -2092,7 +2085,7 @@
           <t>scripts/run_pass1.sh companies-live</t>
         </is>
       </c>
-      <c r="G11" s="14" t="inlineStr">
+      <c r="G11" s="6" t="inlineStr">
         <is>
           <t>Parallel</t>
         </is>
@@ -2133,7 +2126,7 @@
           <t>scripts/run_pass1.sh attach-dry</t>
         </is>
       </c>
-      <c r="G12" s="14" t="inlineStr">
+      <c r="G12" s="6" t="inlineStr">
         <is>
           <t>Parallel</t>
         </is>
@@ -2174,7 +2167,7 @@
           <t>scripts/run_pass1.sh attach-upload</t>
         </is>
       </c>
-      <c r="G13" s="13" t="inlineStr">
+      <c r="G13" s="7" t="inlineStr">
         <is>
           <t>Conditional</t>
         </is>
@@ -2219,7 +2212,7 @@
           <t>scripts/run_pass1.sh attach-notes</t>
         </is>
       </c>
-      <c r="G14" s="13" t="inlineStr">
+      <c r="G14" s="7" t="inlineStr">
         <is>
           <t>Conditional</t>
         </is>
@@ -2264,7 +2257,7 @@
           <t>scripts/run_pass1.sh ledger-export</t>
         </is>
       </c>
-      <c r="G15" s="13" t="inlineStr">
+      <c r="G15" s="7" t="inlineStr">
         <is>
           <t>Conditional</t>
         </is>
@@ -2305,7 +2298,7 @@
           <t>scripts/run_pass1.sh deals-dry</t>
         </is>
       </c>
-      <c r="G16" s="14" t="inlineStr">
+      <c r="G16" s="6" t="inlineStr">
         <is>
           <t>Parallel</t>
         </is>
@@ -2352,7 +2345,7 @@
           <t>scripts/run_pass1.sh ledger-export</t>
         </is>
       </c>
-      <c r="G17" s="13" t="inlineStr">
+      <c r="G17" s="7" t="inlineStr">
         <is>
           <t>Conditional</t>
         </is>
@@ -2395,7 +2388,7 @@
           <t>bq query --use_legacy_sql=false 'SELECT dealname, company_name, company_hs_object_id, op_company_status, op_approve, hs_object_id FROM `wisekeybq.mrload_raw.hubspot_deals_import` ORDER BY company_name, dealname'</t>
         </is>
       </c>
-      <c r="G18" s="14" t="inlineStr">
+      <c r="G18" s="6" t="inlineStr">
         <is>
           <t>Parallel</t>
         </is>
@@ -2440,7 +2433,7 @@
           <t>scripts/run_pass1.sh deals-live</t>
         </is>
       </c>
-      <c r="G19" s="13" t="inlineStr">
+      <c r="G19" s="7" t="inlineStr">
         <is>
           <t>Conditional</t>
         </is>
@@ -2485,7 +2478,7 @@
           <t>scripts/run_pass1.sh ledger-export</t>
         </is>
       </c>
-      <c r="G20" s="13" t="inlineStr">
+      <c r="G20" s="7" t="inlineStr">
         <is>
           <t>Conditional</t>
         </is>
@@ -2526,7 +2519,7 @@
           <t>scripts/run_pass1.sh status; scripts/dev/pipeline_state.sh</t>
         </is>
       </c>
-      <c r="G21" s="14" t="inlineStr">
+      <c r="G21" s="6" t="inlineStr">
         <is>
           <t>Parallel</t>
         </is>
@@ -2571,7 +2564,7 @@
           <t>scripts/run_pass1.sh unmigrate</t>
         </is>
       </c>
-      <c r="G22" s="13" t="inlineStr">
+      <c r="G22" s="7" t="inlineStr">
         <is>
           <t>Conditional</t>
         </is>

--- a/docs/EXECUTION_SURFACES.xlsx
+++ b/docs/EXECUTION_SURFACES.xlsx
@@ -520,10 +520,10 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="120" customHeight="1">
+    <row r="2" ht="150" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Verdict: from the acquisition of the code to the last step, motion A (zip or clone → VS Code → Polyglot notebooks) yields the same artefacts as motions B (WezTerm → Ubuntu terminal) and C (Cloud Shell), because every step cell runs the same scripts/run_pass1.sh inside an Ubuntu that the same bootstrap provisioned, against the same BigQuery project, Drive root and HubSpot portal. The layers that are NOT parallel are all outside the pipeline itself: acquiring and updating the code (a zip has no git), file modes, package provisioning, and the locality of the SQLite ledger for the live HubSpot steps. Each has a remediation in the Layers sheet. Reconciled through pass 2 on 2026-09-30: the orphan salvage (6f38600) and the BigQuery materialisation of the HubSpot import files (765cd01) were run from Cloud Shell and probed with bq query — the table is the same from every surface. See Layers L14–L15, Pipeline steps 15b–15c, Remediation R21–R25, the last four Equality checks, and docs/EXECUTION_SURFACES.md for the narrative.</t>
+          <t>Verdict: from the acquisition of the code to the last step, motion A (zip or clone → VS Code → Polyglot notebooks) yields the same artefacts as motions B (WezTerm → Ubuntu terminal) and C (Cloud Shell), because every step cell runs the same scripts/run_pass1.sh inside an Ubuntu that the same bootstrap provisioned, against the same BigQuery project, Drive root and HubSpot portal. The layers that are NOT parallel are all outside the pipeline itself: acquiring and updating the code (a zip has no git), file modes, package provisioning, and the locality of the SQLite ledger for the live HubSpot steps. Each has a remediation in the Layers sheet. Reconciled through pass 2 on 2026-09-30: the orphan salvage (6f38600) and the BigQuery materialisation of the HubSpot import files (765cd01) were run from Cloud Shell and probed with bq query — the table is the same from every surface. See Layers L14–L15, Pipeline steps 15b–15c, Remediation R21–R25, the last four Equality checks, and docs/EXECUTION_SURFACES.md for the narrative. The API route was completed the same day: after a .env placeholder was replaced by the sandbox pipeline / stage ids, deals-live created 9 deals in the Miraex pipeline, the 4 salvaged ELTA rows included (L16, R26–R28, three new Equality checks).</t>
         </is>
       </c>
     </row>
@@ -779,7 +779,7 @@
     <row r="17" ht="90" customHeight="1">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>Legend: Parity column colours — green Parallel, yellow Conditional, orange Divergent. Layers L0–L15 are the execution layer subdivided from acquisition to updates; Pipeline steps are the 16 runner steps plus the pass-2 wizard route (15b–15c), status and rollback; Remediation is the catalogue of observed and simulated failures (R01–R25); Equality checks lists what to compare between two surfaces after each stage. Source: the mr-load repository on branch claude/mr-load-library-system-dphpbj at 2026-09-30 (765cd01), the Cloud Shell logs shared on 2026-09-14/15, and simulations run in the development container (non-git folder, in-place conversion, relative state dir).</t>
+          <t>Legend: Parity column colours — green Parallel, yellow Conditional, orange Divergent. Layers L0–L16 are the execution layer subdivided from acquisition to updates; Pipeline steps are the 16 runner steps plus the pass-2 wizard route (15b–15c), status and rollback; Remediation is the catalogue of observed and simulated failures (R01–R28); Equality checks lists what to compare between two surfaces after each stage. Source: the mr-load repository on branch claude/mr-load-library-system-dphpbj at 2026-09-30 (765cd01), the Cloud Shell logs shared on 2026-09-14/15, and simulations run in the development container (non-git folder, in-place conversion, relative state dir).</t>
         </is>
       </c>
     </row>
@@ -798,7 +798,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>cloudshell edit .mrload/review/deal_decisions.csv (Cloud Shell Editor, Ctrl+S); or nano; view with column -s, -t &lt; … | less -S; or cloudshell download &lt;file&gt; → edit on the laptop → ⋮ Upload → mv ~/deal_decisions.csv ~/mir-load/.mrload/review/</t>
+          <t>nano on any route. Browser terminal only: cloudshell edit .mrload/review/deal_decisions.csv (Cloud Shell Editor, Ctrl+S) or cloudshell download &lt;file&gt; → edit on the laptop → ⋮ Upload → mv ~/deal_decisions.csv ~/mir-load/.mrload/review/. Over gcloud cloud-shell ssh (WezTerm route) the cloudshell verbs fail ("Cannot send messages to client"): gcloud cloud-shell scp both ways — unverified.</t>
         </is>
       </c>
       <c r="F16" s="7" t="inlineStr">
@@ -1550,7 +1550,7 @@
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>The file is per clone (L9): edit it on the surface that will run deals-dry / deals-live. Cloud Shell has no desktop editor, hence cloudshell edit or the download/upload round trip. column misaligns a row whose quoted field contains a comma (glance only). The writer emits CRLF; the reader accepts LF, CRLF or a mix, so any editor is fine.</t>
+          <t>The file is per clone (L9): edit it on the surface that will run deals-dry / deals-live. The cloudshell verbs are a messenger to the browser page hosting the terminal, so they need the browser terminal (or a reconnected tab); nano works on every route. column misaligns a row whose quoted field contains a comma (glance only). The writer emits CRLF; the reader accepts LF, CRLF or a mix.</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>Cloud Shell run of 2026-09-30: review → edit → deals-dry → ledger-export; the rehearsal flips approve on the same file layout.</t>
+          <t>Cloud Shell runs of 2026-09-30: review → sed/nano → deals-dry → ledger-export; cloudshell download failed over the ssh route (observed), gcloud cloud-shell scp not yet probed.</t>
         </is>
       </c>
     </row>
@@ -1608,6 +1608,53 @@
       <c r="I17" s="4" t="inlineStr">
         <is>
           <t>Probe of 2026-09-30 on the sandbox (portal 49610528) from Cloud Shell: 10 rows = the 10 inferred anchors; 4 ELTA rows salvaged (op_company_status salvaged, company_hs_object_id 35988056623 found by name, never created); 6 resolved from pass 1; op_approve N and hs_object_id NULL everywhere (no deal created yet). Row for row the content of review/hubspot_deals_import.csv (rehearsal check 47: byte-identical load).</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>L16</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>Warehouse project: MRLOAD_BQ_PROJECT vs the gcloud default project</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>The notebook runs the same script inside Ubuntu: gcloud config of that Ubuntu's ADC decides the default project.</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>gcloud config get-value project in the WezTerm tab.</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>gcloud config get-value project in Cloud Shell — observed at wisekeyclourrun until the operator ran gcloud config set project wisekeybq.</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t>Conditional</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>preflight, bq-init pass --project_id="$MRLOAD_BQ_PROJECT" and dbt reads MRLOAD_BQ_PROJECT, but the runner's bq load commands (bq-load, ledger-export) do not pass --project_id: they follow the gcloud default project of that surface. With another project active the load fails on a missing dataset or, if a same-named dataset exists there, lands in the wrong project silently.</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>gcloud config set project $MRLOAD_BQ_PROJECT on every surface (compare with scripts/run_pass1.sh preflight, which prints the project). Proposed, not implemented (awaiting consent): --project_id="$MRLOAD_BQ_PROJECT" on the runner's bq load commands, which turns the row Parallel.</t>
+        </is>
+      </c>
+      <c r="I18" s="4" t="inlineStr">
+        <is>
+          <t>Prompt of the 2026-09-30 Cloud Shell log; code read (runner.py _bq_load_cmd / cmd_bq_load).</t>
         </is>
       </c>
     </row>
@@ -2310,7 +2357,7 @@
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>Reads deal_decisions.csv of that clone (edit it there: L14). Orphan companies are searched by name, never created.</t>
+          <t>Reads deal_decisions.csv of that clone (edit it there: L14). Orphan companies are searched by name, never created. A gate kept in .env makes this dry step LIVE on every surface: prefix MRLOAD_APPROVE_DEAL_CREATE=0 for a true dry run.</t>
         </is>
       </c>
     </row>
@@ -2445,7 +2492,7 @@
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>Ledger-keyed (L9); one deal per inferred anchor. This is the programmatic loader for the salvaged deals too: an approved row whose company was salvaged is created and associated to that company id (no Cloud Function needed). create_error = pipeline / dealstage is not an id of THIS portal (R21).</t>
+          <t>Ledger-keyed (L9); one deal per inferred anchor. This is the programmatic loader for the salvaged deals too: an approved row whose company was salvaged is created and associated to that company id (no Cloud Function needed). create_error = pipeline / dealstage is not an id of THIS portal (R21). 2026-09-30: 10 × create_error 400 caused by &lt;placeholder&gt; ids in .env (R26); after the fix 9 deals created in the Miraex pipeline (portal list), the 4 salvaged ELTA rows among them.</t>
         </is>
       </c>
     </row>
@@ -2591,7 +2638,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3521,7 +3568,7 @@
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>cloudshell edit &lt;file&gt; (Cloud Shell Editor) or nano to edit; column -s, -t &lt; &lt;file&gt; | less -S for a glance; less -S &lt;file&gt; for the exact text; cloudshell download &lt;file&gt; then ⋮ Upload and mv ~/&lt;file&gt; ~/mir-load/.mrload/review/ for a laptop round trip.</t>
+          <t>nano or vim on any route. Browser terminal only: cloudshell edit &lt;file&gt; (Cloud Shell Editor), cloudshell download &lt;file&gt;, ⋮ Upload then mv ~/&lt;file&gt; ~/mir-load/.mrload/review/. Over gcloud cloud-shell ssh: gcloud cloud-shell scp cloudshell:&lt;path&gt; localhost:. and back (unverified). column -s, -t &lt; &lt;file&gt; | less -S for a glance; less -S &lt;file&gt; for the exact text.</t>
         </is>
       </c>
       <c r="G25" s="4" t="inlineStr">
@@ -3564,6 +3611,117 @@
       <c r="G26" s="4" t="inlineStr">
         <is>
           <t>probe 2026-09-30 (row 1: company_name Drafts/pre-PO, id 58614964830)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>R26</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>deals-dry / deals-live: create_error: 400 Client Error on EVERY approved row, salvaged and resolved alike</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>L6</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>A B C</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>MRLOAD_DEAL_PIPELINE / MRLOAD_DEAL_STAGE in .env held the template text &lt;pipeline id&gt; / &lt;stage id&gt;. Non-empty, so the runner's "dealname and dealstage are required" guard passed; HubSpot rejected the value; the client keeps only the status line, not the body naming the field. Not a scope problem (that is a 403).</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>sed -i 's|^MRLOAD_DEAL_PIPELINE=.*|MRLOAD_DEAL_PIPELINE=938985861|; s|^MRLOAD_DEAL_STAGE=.*|MRLOAD_DEAL_STAGE=1445448859|' .env (sandbox Miraex pipeline; ids from GET /crm/v3/pipelines/deals); scripts/dev/env_clinic.sh flags &lt;…&gt; as a placeholder — run it before pass 2; per-row dealstage in deal_decisions.csv. Proposed (awaiting consent): surface HubSpot's error body in create_error.</t>
+        </is>
+      </c>
+      <c r="G27" s="4" t="inlineStr">
+        <is>
+          <t>Cloud Shell 2026-09-30: cause found with grep/python/curl; 9 deals created after the fix (portal list)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>R27</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>cloudshell download / cloudshell edit: "Cannot send messages to client"</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>The cloudshell CLI messages the browser page hosting the terminal. Over gcloud cloud-shell ssh (WezTerm) there is no web client; a disconnected browser tab gives the same error.</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>Use the browser terminal (console panel, shell.cloud.google.com, or the Cloud Shell Editor's terminal) or reload the tab; from ssh use nano and gcloud cloud-shell scp both ways (unverified). Both routes share $HOME, so they can be mixed.</t>
+        </is>
+      </c>
+      <c r="G28" s="4" t="inlineStr">
+        <is>
+          <t>user log 2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>R28</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>bq load in bq-load / ledger-export: Not found: Dataset &lt;other-project&gt;:mrload_raw, or a load into the wrong project</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>L16</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>A B C</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>The runner's bq load commands pass no --project_id, so they follow gcloud's default project (wisekeyclourrun in the 2026-09-30 log), unlike preflight / bq-init / dbt which use MRLOAD_BQ_PROJECT.</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>gcloud config set project $MRLOAD_BQ_PROJECT before the step (preflight prints the project to compare). Proposed, not implemented (awaiting consent): --project_id="$MRLOAD_BQ_PROJECT" on the runner's bq load commands.</t>
+        </is>
+      </c>
+      <c r="G29" s="4" t="inlineStr">
+        <is>
+          <t>code read + the prompt of the 2026-09-30 log (latent; the operator switched projects before ledger-export)</t>
         </is>
       </c>
     </row>
@@ -3578,7 +3736,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3964,6 +4122,86 @@
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>before deals-dry</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>.env placeholders</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>Invoke-Ubuntu 'scripts/dev/env_clinic.sh'</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>scripts/dev/env_clinic.sh</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>no line 'holds a template placeholder'; MRLOAD_DEAL_PIPELINE / MRLOAD_DEAL_STAGE are portal ids or empty (2026-09-30: &lt;stage id&gt; → 400 on every row)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>after deals-live</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>deals in the portal vs the ledger</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>Invoke-Ubuntu 'scripts/run_pass1.sh status'</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>scripts/run_pass1.sh status; the portal's deal list filtered on the pipeline</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>ledger deals_created created=N == N deals in the pipeline (2026-09-30: 9 in Miraex, 2 Closed Won, Drafts/pre-PO absent)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>any time</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>gcloud default project</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>Invoke-Ubuntu 'gcloud config get-value project'</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>gcloud config get-value project</t>
+        </is>
+      </c>
+      <c r="E17" s="4">
+        <f>= MRLOAD_BQ_PROJECT on every surface (bq-load / ledger-export follow it)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
